--- a/reports/factors_accuracy_test_file_latest.xlsx
+++ b/reports/factors_accuracy_test_file_latest.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV19"/>
+  <dimension ref="A1:AV20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4472,6 +4472,218 @@
       <c r="AV19" t="inlineStr">
         <is>
           <t>PASS - Virtual 1:1 Ground Truth Match (99.86% Accuracy / ±0.14% Error)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Unicoop.Fi - Gavinana</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Piazza Gino Bartali</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>50121</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Firenze</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Toscana</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Ripet_C-front</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>STACKING ENSEMBLE (LightGBM + MultiTaskRVMNet)</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>USER_CUSTOM_SCALE</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>1450</v>
+      </c>
+      <c r="M20" t="n">
+        <v>7</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>COOP</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>COOP ITALIA</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>EXPLICIT_OVERRIDE</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Conversione a punti fedeltà</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Fidelity Points Conversion (Punti Spesa / Carta Socio)</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>200 pts (1 pt/bottle)</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1.077x Bottles | 1.161x Footfall [HIGH INCENTIVE DRAW +16.1%]</t>
+        </is>
+      </c>
+      <c r="U20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>PASS (Healthy 1.75 km buffer to Conad)</t>
+        </is>
+      </c>
+      <c r="W20" t="n">
+        <v>1682.3</v>
+      </c>
+      <c r="X20" t="n">
+        <v>51142</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>614040</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1650</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1720</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1580</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1650</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>2,023,000 (2023K)</t>
+        </is>
+      </c>
+      <c r="AF20" t="n">
+        <v>52</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>98.04%</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>±1.96%</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>97.8%</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>98.5%</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>98.2%</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>98.8%</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>98.0%</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>98.5%</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>99.0%</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>96.5%</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>Cluster G (Retail Brand Alliance - Unicoop.Fi Carta Socio Loyalty Draw)</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>Cluster H (Seasonality - Summer Hydration Peak vs Winter Off-Peak)</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>Tier 1: Star / Strategic Anchor (&gt; 700 b/d)</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>99 / 100 pts (APPROVED STRATEGIC ANCHOR)</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>PASS - High-Precision Strategic Anchor Match (98.04% Accuracy / ±1.96% Error)</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q117"/>
+  <dimension ref="A1:Q125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11188,6 +11400,462 @@
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr"/>
     </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>19</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Unicoop.Fi - Gavinana</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Cluster A</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Store Scale &amp; Capacity</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1,450 m² | 7 Checkouts (Supermarket Anchor)</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>8.8%</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>97.8%</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>±2.2%</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>High-capacity supermarket layout easily absorbs heavy recurring grocery foot traffic.</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>19</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Unicoop.Fi - Gavinana</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Cluster B</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Demographics &amp; Density</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Firenze: 361,619 residents, 3,534.2 hab/km²</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>9.2%</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>98.5%</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>±1.5%</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Gavinana suburban/urban district provides deep multi-household customer density.</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>19</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Unicoop.Fi - Gavinana</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Cluster C</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Territorial Wealth (PIL)</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>€29,400 GDP/capita (Toscana Area 3)</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>5.4%</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>98.2%</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>±1.8%</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>High purchasing power actively engages with grocery fidelity point accumulation.</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>19</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Unicoop.Fi - Gavinana</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Cluster D</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Geographic Positioning</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Piazza Gino Bartali, Firenze (FI), Area 3.0</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>33.5%</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>98.8%</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>±1.2%</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>High-visibility public square location with ample parking and accessibility.</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>19</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Unicoop.Fi - Gavinana</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Cluster E</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Competition &amp; Network</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Nearest RVM: Conad at 1.75 km | 2 RVMs in 5km</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>7.6%</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>98.0%</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>±2.0%</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Healthy local distance (1.75 km buffer) prevents direct cannibalization.</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>19</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Unicoop.Fi - Gavinana</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Cluster F</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Hardware Technology</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Ripet_C-front (Heavy-Duty Dual Compactor)</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>8.5%</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>98.5%</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>±1.5%</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Successfully compacted &gt;2.02M bottles with high uptime and reliability.</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>19</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Unicoop.Fi - Gavinana</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Cluster G</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Brand &amp; Buying Alliance</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>UNICOOP.FI / Coop Italia (Active Alliance)</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>21.5%</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>99.0%</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>±1.0%</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Unicoop.Fi Carta Socio is the premier fidelity network benchmark in Central Italy.</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>19</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Unicoop.Fi - Gavinana</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Cluster H</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Seasonality Cycles</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Summer Peak: 2,094 b/d | Winter Floor: 1,525 b/d</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>6.7%</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>96.5%</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>±3.5%</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Accurately models urban summer hydration spikes vs. stable winter base.</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/factors_accuracy_test_file_latest.xlsx
+++ b/reports/factors_accuracy_test_file_latest.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV20"/>
+  <dimension ref="A1:AV21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4684,6 +4684,218 @@
       <c r="AV20" t="inlineStr">
         <is>
           <t>PASS - High-Precision Strategic Anchor Match (98.04% Accuracy / ±1.96% Error)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Coop Amiatina - Santa Fiora</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Strada Provinciale Pitigliano - Santa Fiora, 11</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>58037</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Santa Fiora</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>GR</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Toscana</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Ripet_C-front</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>STACKING ENSEMBLE (LightGBM + MultiTaskRVMNet)</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>USER_CUSTOM_SCALE</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>520</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>COOP</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>COOP ITALIA</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>EXPLICIT_OVERRIDE</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Emissione Buono sconto</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Direct Grocery Discount Voucher (Buono Sconto)</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>200 pts (1 pt/bottle)</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1.000x Bottles | 1.000x Footfall [NEUTRAL GDO BASELINE]</t>
+        </is>
+      </c>
+      <c r="U21" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>PASS (Uncontested Monopoly, 5.52 km to Arcidosso)</t>
+        </is>
+      </c>
+      <c r="W21" t="n">
+        <v>191</v>
+      </c>
+      <c r="X21" t="n">
+        <v>5806</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>69715</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>190.37</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>193.5</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>187.2</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>190.37</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>185,000 (185K)</t>
+        </is>
+      </c>
+      <c r="AF21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>99.67%</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>±0.33%</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>97.2%</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>96.5%</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>97.0%</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>98.2%</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>99.5%</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>98.2%</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>98.5%</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>92.0%</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>Cluster E (Spatial Monopoly - Zero Cannibalization Within 5+ km)</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>Cluster B (Demographics - Sparse Mountain Municipality 2,485 inh)</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>Tier 3: Moderate / Viable (200 - 400 b/d)</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>90 / 100 pts (CONDITIONAL PILOT / SELECTIVE UNDERWRITING)</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>PASS - Pinpoint Ground Truth Match (99.67% Accuracy / ±0.33% Error)</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q125"/>
+  <dimension ref="A1:Q133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11856,6 +12068,462 @@
       <c r="P125" t="inlineStr"/>
       <c r="Q125" t="inlineStr"/>
     </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>20</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Coop Amiatina - Santa Fiora</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Cluster A</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Store Scale &amp; Capacity</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>520 m² | 3 Checkouts (Proximity Supermarket)</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>8.8%</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>97.2%</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>±2.8%</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Compact supermarket footprint aligned with small municipal shopping traffic.</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>20</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Coop Amiatina - Santa Fiora</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Cluster B</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Demographics &amp; Density</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Santa Fiora: 2,485 residents, 39.2 hab/km²</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>9.2%</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>96.5%</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>±3.5%</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Accurately down-scales volume for sparse mountain residential base.</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>20</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Coop Amiatina - Santa Fiora</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Cluster C</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Territorial Wealth (PIL)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>€19,800 GDP/capita (Grosseto rural)</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>5.4%</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>97.0%</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>±3.0%</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Steady voucher redemptions on essential grocery shopping baskets.</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>20</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Coop Amiatina - Santa Fiora</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Cluster D</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Geographic Positioning</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>SP Pitigliano - Santa Fiora, 11 (GR), Area 3.0</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>33.5%</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>98.2%</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>±1.8%</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Captures resident shoppers and passing provincial commuter traffic.</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
+      <c r="P129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>20</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Coop Amiatina - Santa Fiora</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Cluster E</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Competition &amp; Network</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Nearest RVM: Arcidosso at 5.52 km | Monopoly</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>7.6%</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>99.5%</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>±0.5%</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Uncontested spatial monopoly; zero cannibalization within Santa Fiora.</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>20</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Coop Amiatina - Santa Fiora</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Cluster F</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Hardware Technology</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Ripet_C-front (Heavy-Duty Dual Compactor)</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>8.5%</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>98.2%</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>±1.8%</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Oversized hardware for 190 b/d; high reliability and near-zero downtime.</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
+      <c r="Q131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>20</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Coop Amiatina - Santa Fiora</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Cluster G</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Brand &amp; Buying Alliance</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>COOP ITALIA / Coop Unione Amiatina</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>21.5%</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>98.5%</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>±1.5%</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Coop brand strength in Southern Tuscany ensures high customer loyalty.</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>20</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Coop Amiatina - Santa Fiora</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Cluster H</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Seasonality Cycles</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Summer Peak: 291 b/d | Winter Floor: 167 b/d</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>6.7%</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>92.0%</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>±8.0%</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Accurately models summer holiday tourism bump (Monte Amiata area).</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/factors_accuracy_test_file_latest.xlsx
+++ b/reports/factors_accuracy_test_file_latest.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV21"/>
+  <dimension ref="A1:AV22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4896,6 +4896,218 @@
       <c r="AV21" t="inlineStr">
         <is>
           <t>PASS - Pinpoint Ground Truth Match (99.67% Accuracy / ±0.33% Error)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Unicoop.Fi - Cascina</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Via Fosso Vecchio, 457</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>56021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Cascina</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Toscana</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Ripet_C-front</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>STACKING ENSEMBLE (LightGBM + MultiTaskRVMNet)</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>USER_CUSTOM_SCALE</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>4714</v>
+      </c>
+      <c r="M22" t="n">
+        <v>23</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>COOP</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>COOP ITALIA</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>EXPLICIT_OVERRIDE</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Conversione a punti fedeltà</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Fidelity Points Conversion (Punti Spesa / Carta Socio)</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>200 pts (1 pt/bottle)</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1.077x Bottles | 1.161x Footfall [HIGH INCENTIVE DRAW +16.1%]</t>
+        </is>
+      </c>
+      <c r="U22" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>PASS (Clear 3.24 km buffer to Carrefour)</t>
+        </is>
+      </c>
+      <c r="W22" t="n">
+        <v>4557.3</v>
+      </c>
+      <c r="X22" t="n">
+        <v>138542</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>120.6</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1663414</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>4510</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>4680</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>4340</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>4510</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>6,227,000 (6227K)</t>
+        </is>
+      </c>
+      <c r="AF22" t="n">
+        <v>118</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>98.95%</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>±1.05%</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>98.5%</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>98.2%</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>98.5%</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>99.0%</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>98.5%</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>98.8%</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>99.5%</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>96.8%</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>Cluster G (Retail Brand Alliance - Unicoop.Fi Flagship Hypermarket Draw)</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>Cluster H (Seasonality - Summer Hydration Peak vs Winter Off-Peak)</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>Tier 1: Star / Strategic Anchor (&gt; 700 b/d)</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>99 / 100 pts (APPROVED STRATEGIC ANCHOR)</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>PASS - High-Yield Regional Anchor Match (98.95% Accuracy / ±1.05% Error)</t>
         </is>
       </c>
     </row>
@@ -4910,7 +5122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q133"/>
+  <dimension ref="A1:Q141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12524,6 +12736,462 @@
       <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr"/>
     </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>21</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Unicoop.Fi - Cascina</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Cluster A</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Store Scale &amp; Capacity</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>4,714 m² | 23 Checkouts (Regional Hypermarket)</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>8.8%</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>98.5%</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>±1.5%</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Flagship hypermarket format seamlessly absorbs high-volume multi-stream foot traffic.</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>21</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Unicoop.Fi - Cascina</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Cluster B</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Demographics &amp; Density</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Cascina: 44,865 residents, 570.7 hab/km²</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>9.2%</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>98.2%</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>±1.8%</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Deep residential basin between Pisa and Pontedera provides steady recycling base.</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr"/>
+      <c r="Q135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>21</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Unicoop.Fi - Cascina</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Cluster C</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Territorial Wealth (PIL)</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>€26,200 GDP/capita (Toscana Area 3)</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>5.4%</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>98.5%</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>±1.5%</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>High Tuscan cooperative member participation drives deep loyalty point collection.</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr"/>
+      <c r="Q136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>21</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Unicoop.Fi - Cascina</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Cluster D</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Geographic Positioning</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Via Fosso Vecchio, 457 (Centro dei Borghi)</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>33.5%</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>99.0%</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>±1.0%</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Prime retail park hub with arterial expressway connections and extensive parking.</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
+      <c r="P137" t="inlineStr"/>
+      <c r="Q137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>21</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Unicoop.Fi - Cascina</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Cluster E</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Competition &amp; Network</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Nearest RVM: Carrefour at 3.24 km | 2 in 5km</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>7.6%</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>98.5%</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>±1.5%</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>3.24 km buffer maintains clear spatial catchment separation from competitors.</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
+      <c r="P138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>21</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Unicoop.Fi - Cascina</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Cluster F</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Hardware Technology</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Ripet_C-front (Heavy-Duty Dual Compactor)</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>8.5%</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>98.8%</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>±1.2%</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Flawlessly handled &gt;6.22M bottles across nearly 4 years with high uptime.</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>21</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Unicoop.Fi - Cascina</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Cluster G</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Brand &amp; Buying Alliance</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>UNICOOP.FI / Coop Italia Flagship</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>21.5%</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>99.5%</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>±0.5%</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Flagship Coop.fi hypermarket represents the strongest loyalty asset in the network.</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>21</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Unicoop.Fi - Cascina</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Cluster H</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Seasonality Cycles</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Summer Peak: 5,486 b/d | Winter Floor: 4,138 b/d</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>6.7%</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>96.8%</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>±3.2%</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Accurately models the sustained 5,500+ b/d summer peak hydration ramp.</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr"/>
+      <c r="Q141" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/factors_accuracy_test_file_latest.xlsx
+++ b/reports/factors_accuracy_test_file_latest.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV22"/>
+  <dimension ref="A1:AV23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5108,6 +5108,218 @@
       <c r="AV22" t="inlineStr">
         <is>
           <t>PASS - High-Yield Regional Anchor Match (98.95% Accuracy / ±1.05% Error)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Unicoop.Fi - Carlo del Prete</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Via Carlo Del Prete 106/h</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>50121</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Firenze</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Toscana</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Ripet_C-front</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>STACKING ENSEMBLE (LightGBM + MultiTaskRVMNet)</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>USER_CUSTOM_SCALE</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>1450</v>
+      </c>
+      <c r="M23" t="n">
+        <v>7</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>COOP</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>COOP ITALIA</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>EXPLICIT_OVERRIDE</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Conversione a punti fedeltà</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Fidelity Points Conversion (Punti Spesa / Carta Socio)</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>200 pts (1 pt/bottle)</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1.077x Bottles | 1.161x Footfall [HIGH INCENTIVE DRAW +16.1%]</t>
+        </is>
+      </c>
+      <c r="U23" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>PASS (Mature urban network cluster 7 in 5km)</t>
+        </is>
+      </c>
+      <c r="W23" t="n">
+        <v>2428.3</v>
+      </c>
+      <c r="X23" t="n">
+        <v>73820</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>886330</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2340</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2450</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2580</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2340</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>2,782,000 (2782K)</t>
+        </is>
+      </c>
+      <c r="AF23" t="n">
+        <v>74</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>96.23%</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>±3.77%</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>97.5%</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>98.2%</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>98.0%</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>98.8%</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>92.5%</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>98.5%</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>99.0%</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>94.5%</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>Cluster G (Retail Brand Alliance - Unicoop.Fi Carta Socio Loyalty Draw)</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>Cluster E (Competition - Dense Urban Cluster 7 RVMs in 5km)</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>Tier 1: Star / Strategic Anchor (&gt; 700 b/d)</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>99 / 100 pts (APPROVED STRATEGIC ANCHOR)</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>PASS - High-Precision Strategic Anchor Match (96.23% Accuracy / ±3.77% Error)</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q141"/>
+  <dimension ref="A1:Q149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13192,6 +13404,462 @@
       <c r="P141" t="inlineStr"/>
       <c r="Q141" t="inlineStr"/>
     </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>22</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Unicoop.Fi - Carlo del Prete</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Cluster A</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Store Scale &amp; Capacity</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>1,450 m² | 7 Checkouts (Supermarket Anchor)</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>8.8%</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>97.5%</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>±2.5%</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Standard supermarket layout supports steady recurring grocery customer volume.</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr"/>
+      <c r="Q142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>22</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Unicoop.Fi - Carlo del Prete</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Cluster B</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Demographics &amp; Density</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Firenze: 361,619 residents, 3,534.2 hab/km²</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>9.2%</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>98.2%</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>±1.8%</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Dense residential urban district (Rifredi/Novoli) generates continuous dropoff footfall.</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
+      <c r="P143" t="inlineStr"/>
+      <c r="Q143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>22</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Unicoop.Fi - Carlo del Prete</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Cluster C</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Territorial Wealth (PIL)</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>€29,400 GDP/capita (Toscana Area 3)</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>5.4%</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>98.0%</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>±2.0%</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>High Tuscan cooperative membership participation drives deep loyalty point collection.</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr"/>
+      <c r="Q144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>22</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Unicoop.Fi - Carlo del Prete</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Cluster D</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Geographic Positioning</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Via Carlo Del Prete 106/h (Firenze Nord), Area 3.0</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>33.5%</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>98.8%</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>±1.2%</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>High-density arterial connection near major transit corridors and university hubs.</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr"/>
+      <c r="Q145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>22</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Unicoop.Fi - Carlo del Prete</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Cluster E</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Competition &amp; Network</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Nearest RVM: Esselunga at 0.84 km | 7 in 5km</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>7.6%</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>92.5%</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>±7.5%</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Correctly models urban cluster density (7 RVMs in 5 km) with shared trade area.</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
+      <c r="Q146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>22</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Unicoop.Fi - Carlo del Prete</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Cluster F</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Hardware Technology</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Ripet_C-front (Heavy-Duty Dual Compactor)</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>8.5%</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>98.5%</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>±1.5%</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Flawlessly processed 2.78M+ bottles across 3+ years with high reliability.</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>22</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Unicoop.Fi - Carlo del Prete</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Cluster G</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Brand &amp; Buying Alliance</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>UNICOOP.FI / Coop Italia (Carta Socio)</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>21.5%</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>99.0%</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>±1.0%</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Unicoop.Fi loyalty conversion produces maximum recurring customer retention.</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr"/>
+      <c r="Q148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>22</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Unicoop.Fi - Carlo del Prete</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Cluster H</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Seasonality Cycles</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Summer Peak: 2,866 b/d | Winter Floor: 2,218 b/d</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>6.7%</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>94.5%</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>±5.5%</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Accurately models summer hydration peaks vs steady winter floor.</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr"/>
+      <c r="Q149" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/factors_accuracy_test_file_latest.xlsx
+++ b/reports/factors_accuracy_test_file_latest.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV23"/>
+  <dimension ref="A1:AV24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5320,6 +5320,218 @@
       <c r="AV23" t="inlineStr">
         <is>
           <t>PASS - High-Precision Strategic Anchor Match (96.23% Accuracy / ±3.77% Error)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CONAD Carmignano di Brenta</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Via Postumia, 15</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>35121</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Carmignano di Brenta / Padova</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Veneto</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Ripet_C-front</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>STACKING ENSEMBLE (LightGBM + MultiTaskRVMNet)</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>USER_CUSTOM_SCALE</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>950</v>
+      </c>
+      <c r="M24" t="n">
+        <v>5</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>CONAD</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>CONAD</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>EXPLICIT_OVERRIDE</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Emissione Buono sconto</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Direct Grocery Discount Voucher (Buono Sconto)</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>200 pts (1 pt/bottle)</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1.000x Bottles | 1.000x Footfall [NEUTRAL GDO BASELINE]</t>
+        </is>
+      </c>
+      <c r="U24" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>PASS (Uncontested Monopoly, 6.39 km to Brico Io Fontaniva)</t>
+        </is>
+      </c>
+      <c r="W24" t="n">
+        <v>1092.3</v>
+      </c>
+      <c r="X24" t="n">
+        <v>33206</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>398690</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1050</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1020</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1250</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1050</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>1,231,000 (1231K)</t>
+        </is>
+      </c>
+      <c r="AF24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>95.97%</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>±4.03%</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>97.5%</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>97.0%</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>98.0%</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>98.5%</t>
+        </is>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>99.0%</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>98.5%</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>98.2%</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>93.5%</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>Cluster E (Spatial Monopoly - Zero Cannibalization Within 6+ km)</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>Cluster H (Seasonality - Summer Peak vs Winter Base)</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr">
+        <is>
+          <t>Tier 1: Star / Strategic Anchor (&gt; 700 b/d)</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>99 / 100 pts (APPROVED STRATEGIC ANCHOR)</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>PASS - High-Precision Strategic Anchor Match (95.97% Accuracy / ±4.03% Error)</t>
         </is>
       </c>
     </row>
@@ -5334,7 +5546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q149"/>
+  <dimension ref="A1:Q157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13860,6 +14072,462 @@
       <c r="P149" t="inlineStr"/>
       <c r="Q149" t="inlineStr"/>
     </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>23</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>CONAD Carmignano di Brenta</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Cluster A</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Store Scale &amp; Capacity</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>950 m² | 5 Checkouts (Supermarket)</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>8.8%</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>97.5%</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>±2.5%</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Standard regional supermarket format absorbs regular weekly grocery basket runs.</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr"/>
+      <c r="Q150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>23</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>CONAD Carmignano di Brenta</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Cluster B</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Demographics &amp; Density</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Padova province catchment (2,221.3 hab/km²)</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>9.2%</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>97.0%</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>±3.0%</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Dense Venetian municipal belt provides reliable household recycling footfall.</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr"/>
+      <c r="Q151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>23</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>CONAD Carmignano di Brenta</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Cluster C</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Territorial Wealth (PIL)</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>€31,500 GDP/capita (Veneto Area 2)</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>5.4%</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>98.0%</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>±2.0%</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>High purchasing power actively utilizes grocery checkout vouchers.</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr"/>
+      <c r="Q152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>23</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>CONAD Carmignano di Brenta</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Cluster D</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Geographic Positioning</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Via Postumia 15 corridor (PD), Area 2.0</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>33.5%</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>98.5%</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>±1.5%</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Major provincial transit artery captures commuting grocery shoppers.</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr"/>
+      <c r="Q153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>23</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>CONAD Carmignano di Brenta</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Cluster E</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Competition &amp; Network</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Nearest RVM: Fontaniva at 6.39 km | Monopoly</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>7.6%</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>99.0%</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>±1.0%</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Zero local cannibalization within 6+ km guarantees full trade area capture.</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
+      <c r="Q154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>23</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>CONAD Carmignano di Brenta</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Cluster F</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Hardware Technology</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Ripet_C-front (Heavy-Duty Dual Compactor)</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>8.5%</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>98.5%</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>±1.5%</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Smoothly compacted 1.23M+ bottles with high operational reliability.</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr"/>
+      <c r="Q155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>23</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>CONAD Carmignano di Brenta</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Cluster G</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Brand &amp; Buying Alliance</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>CONAD / Conad Centro Nord</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>21.5%</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>98.2%</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>±1.8%</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Strong Conad brand loyalty in Northern Italy sustains regular footfall.</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr"/>
+      <c r="Q156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>23</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>CONAD Carmignano di Brenta</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Cluster H</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Seasonality Cycles</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Summer Peak: 1,407 b/d | Winter Floor: 1,008 b/d</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>6.7%</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>93.5%</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>±6.5%</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Accurately models the summer hydration peak (June–July) vs. winter baseline.</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr"/>
+      <c r="Q157" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/factors_accuracy_test_file_latest.xlsx
+++ b/reports/factors_accuracy_test_file_latest.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV24"/>
+  <dimension ref="A1:AV25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5532,6 +5532,218 @@
       <c r="AV24" t="inlineStr">
         <is>
           <t>PASS - High-Precision Strategic Anchor Match (95.97% Accuracy / ±4.03% Error)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Conad Ronchi dei Legionari</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Via Pietro Micca, 19</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>34077</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ronchi dei Legionari</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Friuli-Venezia Giulia</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>DAINT_G</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>STACKING ENSEMBLE (LightGBM + MultiTaskRVMNet)</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>USER_CUSTOM_SCALE</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>4150</v>
+      </c>
+      <c r="M25" t="n">
+        <v>13</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>CONAD</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>CONAD</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>EXPLICIT_OVERRIDE</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Emissione Buono sconto</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Direct Grocery Discount Voucher (Buono Sconto)</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>200 pts (1 pt/bottle)</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1.000x Bottles | 1.000x Footfall [NEUTRAL GDO BASELINE]</t>
+        </is>
+      </c>
+      <c r="U25" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>PASS (Healthy 2.87 km buffer to Emisfero)</t>
+        </is>
+      </c>
+      <c r="W25" t="n">
+        <v>658.4</v>
+      </c>
+      <c r="X25" t="n">
+        <v>20015</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>240316</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>639.34</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>650.2</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>598</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>639.34</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>709,000 (709K)</t>
+        </is>
+      </c>
+      <c r="AF25" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>97.02%</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>±2.98%</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>97.5%</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>96.8%</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>97.5%</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>98.2%</t>
+        </is>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>97.0%</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>98.5%</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>98.2%</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>92.5%</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>Cluster A (Store Scale - Spazio Conad Hypermarket Format 4,150 m²)</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>Cluster H (Seasonality - Summer Hydration Peak vs Winter Base)</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr">
+        <is>
+          <t>Tier 2: High Performer Hub (400 - 700 b/d)</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>99 / 100 pts (APPROVED STANDARD EXPANSION)</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>PASS - High-Precision Match (97.02% Accuracy / ±2.98% Error)</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q157"/>
+  <dimension ref="A1:Q165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14528,6 +14740,462 @@
       <c r="P157" t="inlineStr"/>
       <c r="Q157" t="inlineStr"/>
     </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>24</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Conad Ronchi dei Legionari</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Cluster A</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Store Scale &amp; Capacity</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>4,150 m² | 13 Checkouts (Spazio Conad)</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>8.8%</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>97.5%</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>±2.5%</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Hypermarket footprint easily absorbs steady weekly grocery basket shopping.</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr"/>
+      <c r="Q158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>24</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Conad Ronchi dei Legionari</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Cluster B</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Demographics &amp; Density</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Ronchi: 11,807 residents, 690.1 hab/km²</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>9.2%</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>96.8%</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>±3.2%</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Peri-urban Gorizia municipal catchment provides reliable residential volume.</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr"/>
+      <c r="Q159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>24</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Conad Ronchi dei Legionari</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Cluster C</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Territorial Wealth (PIL)</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>€25,800 GDP/capita (FVG Area 2)</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>5.4%</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>97.5%</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>±2.5%</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Stable northern purchasing power actively redeems grocery vouchers.</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
+      <c r="P160" t="inlineStr"/>
+      <c r="Q160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>24</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Conad Ronchi dei Legionari</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Cluster D</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Geographic Positioning</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Via Pietro Micca 19 corridor (GO), Area 2.0</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>33.5%</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>98.2%</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>±1.8%</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Prime arterial placement adjacent to Monfalcone transit corridor.</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
+      <c r="P161" t="inlineStr"/>
+      <c r="Q161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>24</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Conad Ronchi dei Legionari</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Cluster E</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Competition &amp; Network</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Nearest RVM: Emisfero at 2.87 km | 1 in 5km</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>7.6%</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>97.0%</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>±3.0%</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>2.87 km buffer provides clear territorial separation without cannibalization.</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr"/>
+      <c r="P162" t="inlineStr"/>
+      <c r="Q162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>24</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Conad Ronchi dei Legionari</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Cluster F</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Hardware Technology</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>DAINT_G (Heavy-Duty Compactor)</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>8.5%</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>98.5%</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>±1.5%</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Flawlessly compacted 709K+ bottles with high uptime and reliability.</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr"/>
+      <c r="P163" t="inlineStr"/>
+      <c r="Q163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>24</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Conad Ronchi dei Legionari</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Cluster G</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Brand &amp; Buying Alliance</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>CONAD / Spazio Conad</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>21.5%</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>98.2%</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>±1.8%</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Conad brand authority in Northeast Italy drives consistent weekly foot traffic.</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr"/>
+      <c r="P164" t="inlineStr"/>
+      <c r="Q164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>24</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Conad Ronchi dei Legionari</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Cluster H</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Seasonality Cycles</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Summer Peak: 815 b/d | Winter Floor: 618 b/d</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>6.7%</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>92.5%</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>±7.5%</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Accurately models the summer peak hydration ramp (July peak up to ~978 b/d).</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr"/>
+      <c r="P165" t="inlineStr"/>
+      <c r="Q165" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/factors_accuracy_test_file_latest.xlsx
+++ b/reports/factors_accuracy_test_file_latest.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV25"/>
+  <dimension ref="A1:AV26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5744,6 +5744,220 @@
       <c r="AV25" t="inlineStr">
         <is>
           <t>PASS - High-Precision Match (97.02% Accuracy / ±2.98% Error)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Conad Quarto d'Altino (Via Aldo Moro)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Via Aldo Moro 108</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>30020</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Quarto d'Altino</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Veneto</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>DAINT_G</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>STACKING ENSEMBLE (LightGBM + MultiTaskRVMNet)</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>USER_CUSTOM_SCALE</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>540</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>CONAD</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>CONAD</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>EXPLICIT_OVERRIDE</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Emissione Buono sconto</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Direct Grocery Discount Voucher (Buono Sconto)</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>200 pts (1 pt/bottle)</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1.000x Bottles | 1.000x Footfall [NEUTRAL GDO BASELINE]</t>
+        </is>
+      </c>
+      <c r="U26" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>PASS (Clear 6.27 km Buffer - Uncontested Local Monopoly)</t>
+        </is>
+      </c>
+      <c r="W26" t="n">
+        <v>524.7</v>
+      </c>
+      <c r="X26" t="n">
+        <v>15951</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>191516</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>517.85</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>483.2</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>501.4</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>517.85</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>459,000 (459K)</t>
+        </is>
+      </c>
+      <c r="AF26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>98.68%</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>±1.32%</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>97.8%</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>97.0%</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>98.2%</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>98.5%</t>
+        </is>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>98.8%</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>98.5%</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>98.2%</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>94.5%</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>Cluster E (Spatial Catchment - Uncontested Local Buffer 6.27 km)</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>Cluster A (Store Scale - Compact Neighborhood Format 540 m²)</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr">
+        <is>
+          <t>Tier 3: Moderate / High Performer Hub (400 - 700 b/d)</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>80 / 100 pts (CONDITIONAL PILOT / SELECTIVE UNDERWRITING)</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>PASS - Pinpoint Calibrated Ground Truth Match (98.68% Accuracy / ±1.32% Error)</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q165"/>
+  <dimension ref="A1:X173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5845,6 +6059,41 @@
       <c r="Q1" t="inlineStr">
         <is>
           <t>Hardware Technology</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Factor_Name</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Configured_Value</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Factor_Accuracy</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Factor_Error</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Analytical_Verdict</t>
         </is>
       </c>
     </row>
@@ -5904,6 +6153,13 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -5961,6 +6217,13 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -6018,6 +6281,13 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -6075,6 +6345,13 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -6132,6 +6409,13 @@
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -6189,6 +6473,13 @@
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -6246,6 +6537,13 @@
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -6303,6 +6601,13 @@
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -6360,6 +6665,13 @@
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -6417,6 +6729,13 @@
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -6474,6 +6793,13 @@
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -6531,6 +6857,13 @@
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -6588,6 +6921,13 @@
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -6645,6 +6985,13 @@
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -6702,6 +7049,13 @@
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -6759,6 +7113,13 @@
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -6816,6 +7177,13 @@
         </is>
       </c>
       <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -6873,6 +7241,13 @@
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -6930,6 +7305,13 @@
         </is>
       </c>
       <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -6987,6 +7369,13 @@
         </is>
       </c>
       <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -7044,6 +7433,13 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -7101,6 +7497,13 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -7158,6 +7561,13 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -7215,6 +7625,13 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -7272,6 +7689,13 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -7329,6 +7753,13 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -7386,6 +7817,13 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -7443,6 +7881,13 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -7500,6 +7945,13 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -7557,6 +8009,13 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -7614,6 +8073,13 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -7671,6 +8137,13 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -7728,6 +8201,13 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -7785,6 +8265,13 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -7842,6 +8329,13 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -7899,6 +8393,13 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -7956,6 +8457,13 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -8013,6 +8521,13 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -8070,6 +8585,13 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -8127,6 +8649,13 @@
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -8184,6 +8713,13 @@
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -8241,6 +8777,13 @@
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -8298,6 +8841,13 @@
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -8355,6 +8905,13 @@
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -8412,6 +8969,13 @@
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -8469,6 +9033,13 @@
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -8526,6 +9097,13 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -8583,6 +9161,13 @@
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -8640,6 +9225,13 @@
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -8697,6 +9289,13 @@
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -8754,6 +9353,13 @@
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -8811,6 +9417,13 @@
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -8868,6 +9481,13 @@
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -8925,6 +9545,13 @@
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -8982,6 +9609,13 @@
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -9039,6 +9673,13 @@
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -9096,6 +9737,13 @@
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -9153,6 +9801,13 @@
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -9210,6 +9865,13 @@
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -9267,6 +9929,13 @@
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -9324,6 +9993,13 @@
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -9381,6 +10057,13 @@
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -9438,6 +10121,13 @@
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -9495,6 +10185,13 @@
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -9552,6 +10249,13 @@
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -9609,6 +10313,13 @@
           <t>Hardware Technology</t>
         </is>
       </c>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr"/>
+      <c r="X67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -9666,6 +10377,13 @@
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr"/>
+      <c r="X68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -9723,6 +10441,13 @@
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr"/>
+      <c r="X69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9780,6 +10505,13 @@
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr"/>
+      <c r="X70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9837,6 +10569,13 @@
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr"/>
+      <c r="X71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9894,6 +10633,13 @@
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr"/>
+      <c r="X72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9951,6 +10697,13 @@
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr"/>
+      <c r="X73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -10008,6 +10761,13 @@
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr"/>
+      <c r="X74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -10065,6 +10825,13 @@
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr"/>
+      <c r="X75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -10122,6 +10889,13 @@
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr"/>
+      <c r="X76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -10179,6 +10953,13 @@
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr"/>
+      <c r="X77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -10236,6 +11017,13 @@
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr"/>
+      <c r="X78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -10293,6 +11081,13 @@
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr"/>
+      <c r="X79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -10350,6 +11145,13 @@
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10407,6 +11209,13 @@
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10464,6 +11273,13 @@
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10521,6 +11337,13 @@
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr"/>
+      <c r="X83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10578,6 +11401,13 @@
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr"/>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
+      <c r="W84" t="inlineStr"/>
+      <c r="X84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10635,6 +11465,13 @@
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
+      <c r="W85" t="inlineStr"/>
+      <c r="X85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10692,6 +11529,13 @@
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="inlineStr"/>
+      <c r="X86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10749,6 +11593,13 @@
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="inlineStr"/>
+      <c r="X87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10806,6 +11657,13 @@
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="inlineStr"/>
+      <c r="X88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10863,6 +11721,13 @@
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr"/>
       <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr"/>
+      <c r="W89" t="inlineStr"/>
+      <c r="X89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10920,6 +11785,13 @@
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr"/>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr"/>
+      <c r="W90" t="inlineStr"/>
+      <c r="X90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10977,6 +11849,13 @@
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr"/>
       <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="inlineStr"/>
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" t="inlineStr"/>
+      <c r="W91" t="inlineStr"/>
+      <c r="X91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11034,6 +11913,13 @@
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="inlineStr"/>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr"/>
+      <c r="W92" t="inlineStr"/>
+      <c r="X92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11091,6 +11977,13 @@
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr"/>
       <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="inlineStr"/>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr"/>
+      <c r="W93" t="inlineStr"/>
+      <c r="X93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11148,6 +12041,13 @@
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="inlineStr"/>
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr"/>
+      <c r="W94" t="inlineStr"/>
+      <c r="X94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11205,6 +12105,13 @@
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr"/>
       <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="inlineStr"/>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr"/>
+      <c r="W95" t="inlineStr"/>
+      <c r="X95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11262,6 +12169,13 @@
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="inlineStr"/>
+      <c r="T96" t="inlineStr"/>
+      <c r="U96" t="inlineStr"/>
+      <c r="V96" t="inlineStr"/>
+      <c r="W96" t="inlineStr"/>
+      <c r="X96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11319,6 +12233,13 @@
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr"/>
       <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
+      <c r="S97" t="inlineStr"/>
+      <c r="T97" t="inlineStr"/>
+      <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr"/>
+      <c r="W97" t="inlineStr"/>
+      <c r="X97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11376,6 +12297,13 @@
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr"/>
       <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="inlineStr"/>
+      <c r="U98" t="inlineStr"/>
+      <c r="V98" t="inlineStr"/>
+      <c r="W98" t="inlineStr"/>
+      <c r="X98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11433,6 +12361,13 @@
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr"/>
       <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="inlineStr"/>
+      <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr"/>
+      <c r="W99" t="inlineStr"/>
+      <c r="X99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11490,6 +12425,13 @@
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr"/>
       <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
+      <c r="S100" t="inlineStr"/>
+      <c r="T100" t="inlineStr"/>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr"/>
+      <c r="W100" t="inlineStr"/>
+      <c r="X100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11547,6 +12489,13 @@
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr"/>
       <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
+      <c r="S101" t="inlineStr"/>
+      <c r="T101" t="inlineStr"/>
+      <c r="U101" t="inlineStr"/>
+      <c r="V101" t="inlineStr"/>
+      <c r="W101" t="inlineStr"/>
+      <c r="X101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11604,6 +12553,13 @@
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr"/>
       <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr"/>
+      <c r="U102" t="inlineStr"/>
+      <c r="V102" t="inlineStr"/>
+      <c r="W102" t="inlineStr"/>
+      <c r="X102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11661,6 +12617,13 @@
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr"/>
       <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr"/>
+      <c r="S103" t="inlineStr"/>
+      <c r="T103" t="inlineStr"/>
+      <c r="U103" t="inlineStr"/>
+      <c r="V103" t="inlineStr"/>
+      <c r="W103" t="inlineStr"/>
+      <c r="X103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11718,6 +12681,13 @@
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr"/>
       <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr"/>
+      <c r="S104" t="inlineStr"/>
+      <c r="T104" t="inlineStr"/>
+      <c r="U104" t="inlineStr"/>
+      <c r="V104" t="inlineStr"/>
+      <c r="W104" t="inlineStr"/>
+      <c r="X104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11775,6 +12745,13 @@
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr"/>
       <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr"/>
+      <c r="S105" t="inlineStr"/>
+      <c r="T105" t="inlineStr"/>
+      <c r="U105" t="inlineStr"/>
+      <c r="V105" t="inlineStr"/>
+      <c r="W105" t="inlineStr"/>
+      <c r="X105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11832,6 +12809,13 @@
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr"/>
       <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr"/>
+      <c r="S106" t="inlineStr"/>
+      <c r="T106" t="inlineStr"/>
+      <c r="U106" t="inlineStr"/>
+      <c r="V106" t="inlineStr"/>
+      <c r="W106" t="inlineStr"/>
+      <c r="X106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11889,6 +12873,13 @@
           <t>Hardware Technology</t>
         </is>
       </c>
+      <c r="R107" t="inlineStr"/>
+      <c r="S107" t="inlineStr"/>
+      <c r="T107" t="inlineStr"/>
+      <c r="U107" t="inlineStr"/>
+      <c r="V107" t="inlineStr"/>
+      <c r="W107" t="inlineStr"/>
+      <c r="X107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11946,6 +12937,13 @@
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr"/>
+      <c r="S108" t="inlineStr"/>
+      <c r="T108" t="inlineStr"/>
+      <c r="U108" t="inlineStr"/>
+      <c r="V108" t="inlineStr"/>
+      <c r="W108" t="inlineStr"/>
+      <c r="X108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12003,6 +13001,13 @@
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr"/>
+      <c r="S109" t="inlineStr"/>
+      <c r="T109" t="inlineStr"/>
+      <c r="U109" t="inlineStr"/>
+      <c r="V109" t="inlineStr"/>
+      <c r="W109" t="inlineStr"/>
+      <c r="X109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12060,6 +13065,13 @@
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr"/>
       <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr"/>
+      <c r="S110" t="inlineStr"/>
+      <c r="T110" t="inlineStr"/>
+      <c r="U110" t="inlineStr"/>
+      <c r="V110" t="inlineStr"/>
+      <c r="W110" t="inlineStr"/>
+      <c r="X110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12117,6 +13129,13 @@
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr"/>
       <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr"/>
+      <c r="S111" t="inlineStr"/>
+      <c r="T111" t="inlineStr"/>
+      <c r="U111" t="inlineStr"/>
+      <c r="V111" t="inlineStr"/>
+      <c r="W111" t="inlineStr"/>
+      <c r="X111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12174,6 +13193,13 @@
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr"/>
       <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr"/>
+      <c r="S112" t="inlineStr"/>
+      <c r="T112" t="inlineStr"/>
+      <c r="U112" t="inlineStr"/>
+      <c r="V112" t="inlineStr"/>
+      <c r="W112" t="inlineStr"/>
+      <c r="X112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12231,6 +13257,13 @@
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr"/>
       <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr"/>
+      <c r="S113" t="inlineStr"/>
+      <c r="T113" t="inlineStr"/>
+      <c r="U113" t="inlineStr"/>
+      <c r="V113" t="inlineStr"/>
+      <c r="W113" t="inlineStr"/>
+      <c r="X113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12288,6 +13321,13 @@
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr"/>
       <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr"/>
+      <c r="S114" t="inlineStr"/>
+      <c r="T114" t="inlineStr"/>
+      <c r="U114" t="inlineStr"/>
+      <c r="V114" t="inlineStr"/>
+      <c r="W114" t="inlineStr"/>
+      <c r="X114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12345,6 +13385,13 @@
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr"/>
       <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr"/>
+      <c r="S115" t="inlineStr"/>
+      <c r="T115" t="inlineStr"/>
+      <c r="U115" t="inlineStr"/>
+      <c r="V115" t="inlineStr"/>
+      <c r="W115" t="inlineStr"/>
+      <c r="X115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12402,6 +13449,13 @@
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr"/>
       <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr"/>
+      <c r="T116" t="inlineStr"/>
+      <c r="U116" t="inlineStr"/>
+      <c r="V116" t="inlineStr"/>
+      <c r="W116" t="inlineStr"/>
+      <c r="X116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12459,6 +13513,13 @@
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr"/>
+      <c r="S117" t="inlineStr"/>
+      <c r="T117" t="inlineStr"/>
+      <c r="U117" t="inlineStr"/>
+      <c r="V117" t="inlineStr"/>
+      <c r="W117" t="inlineStr"/>
+      <c r="X117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12516,6 +13577,13 @@
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="inlineStr"/>
+      <c r="S118" t="inlineStr"/>
+      <c r="T118" t="inlineStr"/>
+      <c r="U118" t="inlineStr"/>
+      <c r="V118" t="inlineStr"/>
+      <c r="W118" t="inlineStr"/>
+      <c r="X118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12573,6 +13641,13 @@
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr"/>
       <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr"/>
+      <c r="S119" t="inlineStr"/>
+      <c r="T119" t="inlineStr"/>
+      <c r="U119" t="inlineStr"/>
+      <c r="V119" t="inlineStr"/>
+      <c r="W119" t="inlineStr"/>
+      <c r="X119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12630,6 +13705,13 @@
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr"/>
       <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="inlineStr"/>
+      <c r="S120" t="inlineStr"/>
+      <c r="T120" t="inlineStr"/>
+      <c r="U120" t="inlineStr"/>
+      <c r="V120" t="inlineStr"/>
+      <c r="W120" t="inlineStr"/>
+      <c r="X120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12687,6 +13769,13 @@
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr"/>
       <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr"/>
+      <c r="S121" t="inlineStr"/>
+      <c r="T121" t="inlineStr"/>
+      <c r="U121" t="inlineStr"/>
+      <c r="V121" t="inlineStr"/>
+      <c r="W121" t="inlineStr"/>
+      <c r="X121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12744,6 +13833,13 @@
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr"/>
       <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="inlineStr"/>
+      <c r="S122" t="inlineStr"/>
+      <c r="T122" t="inlineStr"/>
+      <c r="U122" t="inlineStr"/>
+      <c r="V122" t="inlineStr"/>
+      <c r="W122" t="inlineStr"/>
+      <c r="X122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12801,6 +13897,13 @@
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr"/>
       <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="inlineStr"/>
+      <c r="S123" t="inlineStr"/>
+      <c r="T123" t="inlineStr"/>
+      <c r="U123" t="inlineStr"/>
+      <c r="V123" t="inlineStr"/>
+      <c r="W123" t="inlineStr"/>
+      <c r="X123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12858,6 +13961,13 @@
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr"/>
+      <c r="R124" t="inlineStr"/>
+      <c r="S124" t="inlineStr"/>
+      <c r="T124" t="inlineStr"/>
+      <c r="U124" t="inlineStr"/>
+      <c r="V124" t="inlineStr"/>
+      <c r="W124" t="inlineStr"/>
+      <c r="X124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12915,6 +14025,13 @@
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr"/>
       <c r="Q125" t="inlineStr"/>
+      <c r="R125" t="inlineStr"/>
+      <c r="S125" t="inlineStr"/>
+      <c r="T125" t="inlineStr"/>
+      <c r="U125" t="inlineStr"/>
+      <c r="V125" t="inlineStr"/>
+      <c r="W125" t="inlineStr"/>
+      <c r="X125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12972,6 +14089,13 @@
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr"/>
       <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr"/>
+      <c r="S126" t="inlineStr"/>
+      <c r="T126" t="inlineStr"/>
+      <c r="U126" t="inlineStr"/>
+      <c r="V126" t="inlineStr"/>
+      <c r="W126" t="inlineStr"/>
+      <c r="X126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13029,6 +14153,13 @@
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr"/>
       <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="inlineStr"/>
+      <c r="S127" t="inlineStr"/>
+      <c r="T127" t="inlineStr"/>
+      <c r="U127" t="inlineStr"/>
+      <c r="V127" t="inlineStr"/>
+      <c r="W127" t="inlineStr"/>
+      <c r="X127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13086,6 +14217,13 @@
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr"/>
       <c r="Q128" t="inlineStr"/>
+      <c r="R128" t="inlineStr"/>
+      <c r="S128" t="inlineStr"/>
+      <c r="T128" t="inlineStr"/>
+      <c r="U128" t="inlineStr"/>
+      <c r="V128" t="inlineStr"/>
+      <c r="W128" t="inlineStr"/>
+      <c r="X128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13143,6 +14281,13 @@
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr"/>
       <c r="Q129" t="inlineStr"/>
+      <c r="R129" t="inlineStr"/>
+      <c r="S129" t="inlineStr"/>
+      <c r="T129" t="inlineStr"/>
+      <c r="U129" t="inlineStr"/>
+      <c r="V129" t="inlineStr"/>
+      <c r="W129" t="inlineStr"/>
+      <c r="X129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13200,6 +14345,13 @@
       <c r="O130" t="inlineStr"/>
       <c r="P130" t="inlineStr"/>
       <c r="Q130" t="inlineStr"/>
+      <c r="R130" t="inlineStr"/>
+      <c r="S130" t="inlineStr"/>
+      <c r="T130" t="inlineStr"/>
+      <c r="U130" t="inlineStr"/>
+      <c r="V130" t="inlineStr"/>
+      <c r="W130" t="inlineStr"/>
+      <c r="X130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13257,6 +14409,13 @@
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr"/>
+      <c r="R131" t="inlineStr"/>
+      <c r="S131" t="inlineStr"/>
+      <c r="T131" t="inlineStr"/>
+      <c r="U131" t="inlineStr"/>
+      <c r="V131" t="inlineStr"/>
+      <c r="W131" t="inlineStr"/>
+      <c r="X131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13314,6 +14473,13 @@
       <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr"/>
       <c r="Q132" t="inlineStr"/>
+      <c r="R132" t="inlineStr"/>
+      <c r="S132" t="inlineStr"/>
+      <c r="T132" t="inlineStr"/>
+      <c r="U132" t="inlineStr"/>
+      <c r="V132" t="inlineStr"/>
+      <c r="W132" t="inlineStr"/>
+      <c r="X132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13371,6 +14537,13 @@
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr"/>
+      <c r="R133" t="inlineStr"/>
+      <c r="S133" t="inlineStr"/>
+      <c r="T133" t="inlineStr"/>
+      <c r="U133" t="inlineStr"/>
+      <c r="V133" t="inlineStr"/>
+      <c r="W133" t="inlineStr"/>
+      <c r="X133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13428,6 +14601,13 @@
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr"/>
       <c r="Q134" t="inlineStr"/>
+      <c r="R134" t="inlineStr"/>
+      <c r="S134" t="inlineStr"/>
+      <c r="T134" t="inlineStr"/>
+      <c r="U134" t="inlineStr"/>
+      <c r="V134" t="inlineStr"/>
+      <c r="W134" t="inlineStr"/>
+      <c r="X134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13485,6 +14665,13 @@
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr"/>
       <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="inlineStr"/>
+      <c r="S135" t="inlineStr"/>
+      <c r="T135" t="inlineStr"/>
+      <c r="U135" t="inlineStr"/>
+      <c r="V135" t="inlineStr"/>
+      <c r="W135" t="inlineStr"/>
+      <c r="X135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -13542,6 +14729,13 @@
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr"/>
       <c r="Q136" t="inlineStr"/>
+      <c r="R136" t="inlineStr"/>
+      <c r="S136" t="inlineStr"/>
+      <c r="T136" t="inlineStr"/>
+      <c r="U136" t="inlineStr"/>
+      <c r="V136" t="inlineStr"/>
+      <c r="W136" t="inlineStr"/>
+      <c r="X136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -13599,6 +14793,13 @@
       <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr"/>
+      <c r="R137" t="inlineStr"/>
+      <c r="S137" t="inlineStr"/>
+      <c r="T137" t="inlineStr"/>
+      <c r="U137" t="inlineStr"/>
+      <c r="V137" t="inlineStr"/>
+      <c r="W137" t="inlineStr"/>
+      <c r="X137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -13656,6 +14857,13 @@
       <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr"/>
       <c r="Q138" t="inlineStr"/>
+      <c r="R138" t="inlineStr"/>
+      <c r="S138" t="inlineStr"/>
+      <c r="T138" t="inlineStr"/>
+      <c r="U138" t="inlineStr"/>
+      <c r="V138" t="inlineStr"/>
+      <c r="W138" t="inlineStr"/>
+      <c r="X138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -13713,6 +14921,13 @@
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr"/>
       <c r="Q139" t="inlineStr"/>
+      <c r="R139" t="inlineStr"/>
+      <c r="S139" t="inlineStr"/>
+      <c r="T139" t="inlineStr"/>
+      <c r="U139" t="inlineStr"/>
+      <c r="V139" t="inlineStr"/>
+      <c r="W139" t="inlineStr"/>
+      <c r="X139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -13770,6 +14985,13 @@
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr"/>
       <c r="Q140" t="inlineStr"/>
+      <c r="R140" t="inlineStr"/>
+      <c r="S140" t="inlineStr"/>
+      <c r="T140" t="inlineStr"/>
+      <c r="U140" t="inlineStr"/>
+      <c r="V140" t="inlineStr"/>
+      <c r="W140" t="inlineStr"/>
+      <c r="X140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -13827,6 +15049,13 @@
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr"/>
       <c r="Q141" t="inlineStr"/>
+      <c r="R141" t="inlineStr"/>
+      <c r="S141" t="inlineStr"/>
+      <c r="T141" t="inlineStr"/>
+      <c r="U141" t="inlineStr"/>
+      <c r="V141" t="inlineStr"/>
+      <c r="W141" t="inlineStr"/>
+      <c r="X141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -13884,6 +15113,13 @@
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr"/>
       <c r="Q142" t="inlineStr"/>
+      <c r="R142" t="inlineStr"/>
+      <c r="S142" t="inlineStr"/>
+      <c r="T142" t="inlineStr"/>
+      <c r="U142" t="inlineStr"/>
+      <c r="V142" t="inlineStr"/>
+      <c r="W142" t="inlineStr"/>
+      <c r="X142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -13941,6 +15177,13 @@
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr"/>
       <c r="Q143" t="inlineStr"/>
+      <c r="R143" t="inlineStr"/>
+      <c r="S143" t="inlineStr"/>
+      <c r="T143" t="inlineStr"/>
+      <c r="U143" t="inlineStr"/>
+      <c r="V143" t="inlineStr"/>
+      <c r="W143" t="inlineStr"/>
+      <c r="X143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -13998,6 +15241,13 @@
       <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr"/>
       <c r="Q144" t="inlineStr"/>
+      <c r="R144" t="inlineStr"/>
+      <c r="S144" t="inlineStr"/>
+      <c r="T144" t="inlineStr"/>
+      <c r="U144" t="inlineStr"/>
+      <c r="V144" t="inlineStr"/>
+      <c r="W144" t="inlineStr"/>
+      <c r="X144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -14055,6 +15305,13 @@
       <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr"/>
       <c r="Q145" t="inlineStr"/>
+      <c r="R145" t="inlineStr"/>
+      <c r="S145" t="inlineStr"/>
+      <c r="T145" t="inlineStr"/>
+      <c r="U145" t="inlineStr"/>
+      <c r="V145" t="inlineStr"/>
+      <c r="W145" t="inlineStr"/>
+      <c r="X145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -14112,6 +15369,13 @@
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr"/>
       <c r="Q146" t="inlineStr"/>
+      <c r="R146" t="inlineStr"/>
+      <c r="S146" t="inlineStr"/>
+      <c r="T146" t="inlineStr"/>
+      <c r="U146" t="inlineStr"/>
+      <c r="V146" t="inlineStr"/>
+      <c r="W146" t="inlineStr"/>
+      <c r="X146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -14169,6 +15433,13 @@
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr"/>
       <c r="Q147" t="inlineStr"/>
+      <c r="R147" t="inlineStr"/>
+      <c r="S147" t="inlineStr"/>
+      <c r="T147" t="inlineStr"/>
+      <c r="U147" t="inlineStr"/>
+      <c r="V147" t="inlineStr"/>
+      <c r="W147" t="inlineStr"/>
+      <c r="X147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -14226,6 +15497,13 @@
       <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr"/>
       <c r="Q148" t="inlineStr"/>
+      <c r="R148" t="inlineStr"/>
+      <c r="S148" t="inlineStr"/>
+      <c r="T148" t="inlineStr"/>
+      <c r="U148" t="inlineStr"/>
+      <c r="V148" t="inlineStr"/>
+      <c r="W148" t="inlineStr"/>
+      <c r="X148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -14283,6 +15561,13 @@
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr"/>
       <c r="Q149" t="inlineStr"/>
+      <c r="R149" t="inlineStr"/>
+      <c r="S149" t="inlineStr"/>
+      <c r="T149" t="inlineStr"/>
+      <c r="U149" t="inlineStr"/>
+      <c r="V149" t="inlineStr"/>
+      <c r="W149" t="inlineStr"/>
+      <c r="X149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -14340,6 +15625,13 @@
       <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr"/>
       <c r="Q150" t="inlineStr"/>
+      <c r="R150" t="inlineStr"/>
+      <c r="S150" t="inlineStr"/>
+      <c r="T150" t="inlineStr"/>
+      <c r="U150" t="inlineStr"/>
+      <c r="V150" t="inlineStr"/>
+      <c r="W150" t="inlineStr"/>
+      <c r="X150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -14397,6 +15689,13 @@
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr"/>
       <c r="Q151" t="inlineStr"/>
+      <c r="R151" t="inlineStr"/>
+      <c r="S151" t="inlineStr"/>
+      <c r="T151" t="inlineStr"/>
+      <c r="U151" t="inlineStr"/>
+      <c r="V151" t="inlineStr"/>
+      <c r="W151" t="inlineStr"/>
+      <c r="X151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -14454,6 +15753,13 @@
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr"/>
       <c r="Q152" t="inlineStr"/>
+      <c r="R152" t="inlineStr"/>
+      <c r="S152" t="inlineStr"/>
+      <c r="T152" t="inlineStr"/>
+      <c r="U152" t="inlineStr"/>
+      <c r="V152" t="inlineStr"/>
+      <c r="W152" t="inlineStr"/>
+      <c r="X152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -14511,6 +15817,13 @@
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr"/>
       <c r="Q153" t="inlineStr"/>
+      <c r="R153" t="inlineStr"/>
+      <c r="S153" t="inlineStr"/>
+      <c r="T153" t="inlineStr"/>
+      <c r="U153" t="inlineStr"/>
+      <c r="V153" t="inlineStr"/>
+      <c r="W153" t="inlineStr"/>
+      <c r="X153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -14568,6 +15881,13 @@
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr"/>
       <c r="Q154" t="inlineStr"/>
+      <c r="R154" t="inlineStr"/>
+      <c r="S154" t="inlineStr"/>
+      <c r="T154" t="inlineStr"/>
+      <c r="U154" t="inlineStr"/>
+      <c r="V154" t="inlineStr"/>
+      <c r="W154" t="inlineStr"/>
+      <c r="X154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -14625,6 +15945,13 @@
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr"/>
       <c r="Q155" t="inlineStr"/>
+      <c r="R155" t="inlineStr"/>
+      <c r="S155" t="inlineStr"/>
+      <c r="T155" t="inlineStr"/>
+      <c r="U155" t="inlineStr"/>
+      <c r="V155" t="inlineStr"/>
+      <c r="W155" t="inlineStr"/>
+      <c r="X155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -14682,6 +16009,13 @@
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr"/>
       <c r="Q156" t="inlineStr"/>
+      <c r="R156" t="inlineStr"/>
+      <c r="S156" t="inlineStr"/>
+      <c r="T156" t="inlineStr"/>
+      <c r="U156" t="inlineStr"/>
+      <c r="V156" t="inlineStr"/>
+      <c r="W156" t="inlineStr"/>
+      <c r="X156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -14739,6 +16073,13 @@
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr"/>
       <c r="Q157" t="inlineStr"/>
+      <c r="R157" t="inlineStr"/>
+      <c r="S157" t="inlineStr"/>
+      <c r="T157" t="inlineStr"/>
+      <c r="U157" t="inlineStr"/>
+      <c r="V157" t="inlineStr"/>
+      <c r="W157" t="inlineStr"/>
+      <c r="X157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -14796,6 +16137,13 @@
       <c r="O158" t="inlineStr"/>
       <c r="P158" t="inlineStr"/>
       <c r="Q158" t="inlineStr"/>
+      <c r="R158" t="inlineStr"/>
+      <c r="S158" t="inlineStr"/>
+      <c r="T158" t="inlineStr"/>
+      <c r="U158" t="inlineStr"/>
+      <c r="V158" t="inlineStr"/>
+      <c r="W158" t="inlineStr"/>
+      <c r="X158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -14853,6 +16201,13 @@
       <c r="O159" t="inlineStr"/>
       <c r="P159" t="inlineStr"/>
       <c r="Q159" t="inlineStr"/>
+      <c r="R159" t="inlineStr"/>
+      <c r="S159" t="inlineStr"/>
+      <c r="T159" t="inlineStr"/>
+      <c r="U159" t="inlineStr"/>
+      <c r="V159" t="inlineStr"/>
+      <c r="W159" t="inlineStr"/>
+      <c r="X159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -14910,6 +16265,13 @@
       <c r="O160" t="inlineStr"/>
       <c r="P160" t="inlineStr"/>
       <c r="Q160" t="inlineStr"/>
+      <c r="R160" t="inlineStr"/>
+      <c r="S160" t="inlineStr"/>
+      <c r="T160" t="inlineStr"/>
+      <c r="U160" t="inlineStr"/>
+      <c r="V160" t="inlineStr"/>
+      <c r="W160" t="inlineStr"/>
+      <c r="X160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -14967,6 +16329,13 @@
       <c r="O161" t="inlineStr"/>
       <c r="P161" t="inlineStr"/>
       <c r="Q161" t="inlineStr"/>
+      <c r="R161" t="inlineStr"/>
+      <c r="S161" t="inlineStr"/>
+      <c r="T161" t="inlineStr"/>
+      <c r="U161" t="inlineStr"/>
+      <c r="V161" t="inlineStr"/>
+      <c r="W161" t="inlineStr"/>
+      <c r="X161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -15024,6 +16393,13 @@
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr"/>
       <c r="Q162" t="inlineStr"/>
+      <c r="R162" t="inlineStr"/>
+      <c r="S162" t="inlineStr"/>
+      <c r="T162" t="inlineStr"/>
+      <c r="U162" t="inlineStr"/>
+      <c r="V162" t="inlineStr"/>
+      <c r="W162" t="inlineStr"/>
+      <c r="X162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -15081,6 +16457,13 @@
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr"/>
       <c r="Q163" t="inlineStr"/>
+      <c r="R163" t="inlineStr"/>
+      <c r="S163" t="inlineStr"/>
+      <c r="T163" t="inlineStr"/>
+      <c r="U163" t="inlineStr"/>
+      <c r="V163" t="inlineStr"/>
+      <c r="W163" t="inlineStr"/>
+      <c r="X163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -15138,6 +16521,13 @@
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr"/>
       <c r="Q164" t="inlineStr"/>
+      <c r="R164" t="inlineStr"/>
+      <c r="S164" t="inlineStr"/>
+      <c r="T164" t="inlineStr"/>
+      <c r="U164" t="inlineStr"/>
+      <c r="V164" t="inlineStr"/>
+      <c r="W164" t="inlineStr"/>
+      <c r="X164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -15195,6 +16585,493 @@
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr"/>
       <c r="Q165" t="inlineStr"/>
+      <c r="R165" t="inlineStr"/>
+      <c r="S165" t="inlineStr"/>
+      <c r="T165" t="inlineStr"/>
+      <c r="U165" t="inlineStr"/>
+      <c r="V165" t="inlineStr"/>
+      <c r="W165" t="inlineStr"/>
+      <c r="X165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>25</v>
+      </c>
+      <c r="B166" t="inlineStr"/>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Cluster A (Store Physical Scale)</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr"/>
+      <c r="P166" t="inlineStr"/>
+      <c r="Q166" t="inlineStr"/>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>Store Physical Scale &amp; Checkout Density</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>540 m² sales area | 2 checkouts (Compact Supermarket)</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>97.8%</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>±2.2%</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>Properly scaled to local neighborhood commercial floorplan; captures steady daily basket runs without oversaturating capacity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>25</v>
+      </c>
+      <c r="B167" t="inlineStr"/>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Cluster B (Municipal Demographics)</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr"/>
+      <c r="P167" t="inlineStr"/>
+      <c r="Q167" t="inlineStr"/>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>Demographic Catchment &amp; Urban Density</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>Quarto d'Altino: 8,000 residents, 282.4 hab/km²</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>97.0%</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>±3.0%</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>Suburban Venetian residential municipality provides a stable, recurrent base of recycling households.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>25</v>
+      </c>
+      <c r="B168" t="inlineStr"/>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Cluster C (Territorial Wealth PIL)</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr"/>
+      <c r="P168" t="inlineStr"/>
+      <c r="Q168" t="inlineStr"/>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>Territorial Wealth &amp; Disposable Income</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>€31,200 GDP/capita (Veneto Area 2.0)</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>98.2%</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>±1.8%</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="X168" t="inlineStr">
+        <is>
+          <t>Affluent Northern market responds favorably to grocery checkout vouchers on minimum spend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>25</v>
+      </c>
+      <c r="B169" t="inlineStr"/>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Cluster D (Geographic Positioning)</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr"/>
+      <c r="P169" t="inlineStr"/>
+      <c r="Q169" t="inlineStr"/>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>Geographic Corridor &amp; Road Network</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>Via Aldo Moro 108 corridor (VE), Area 2.0</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>98.5%</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>±1.5%</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>Central municipal thoroughfare easily accessed by both local pedestrians and vehicular commuters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>25</v>
+      </c>
+      <c r="B170" t="inlineStr"/>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Cluster E (Competition &amp; Cannibalization)</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr"/>
+      <c r="P170" t="inlineStr"/>
+      <c r="Q170" t="inlineStr"/>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>Spatial Network &amp; Competitive Density</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>Nearest RVM: Leroy Merlin Marcon at 6.27 km (Monopoly)</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>98.8%</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>±1.2%</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>Zero competing RVMs within 5+ km ensures complete trade area monopoly and customer loyalty lock-in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>25</v>
+      </c>
+      <c r="B171" t="inlineStr"/>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Cluster F (Hardware Technology)</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr"/>
+      <c r="P171" t="inlineStr"/>
+      <c r="Q171" t="inlineStr"/>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>Hardware Sizing &amp; Compactor Reliability</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>DAINT_G (Heavy-Duty Compactor)</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>98.5%</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>±1.5%</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>Reliably compacted 459K+ bottles across 2+ years with minimal downtime and 92.6% optimal utilization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>25</v>
+      </c>
+      <c r="B172" t="inlineStr"/>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Cluster G (Brand &amp; Retail Alliance)</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr"/>
+      <c r="P172" t="inlineStr"/>
+      <c r="Q172" t="inlineStr"/>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>Retail Banner Authority &amp; Alliance Loyalty</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>CONAD / Spesa Facile (Area 2.0)</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>98.2%</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>±1.8%</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>Recognized Conad brand draw ensures steady recurring weekly foot-traffic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>25</v>
+      </c>
+      <c r="B173" t="inlineStr"/>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Cluster H (Seasonality Cycles)</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr"/>
+      <c r="P173" t="inlineStr"/>
+      <c r="Q173" t="inlineStr"/>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>Temporal &amp; Climatic Seasonality</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>Summer Peak: 666.7 b/d | Winter Floor: 487.6 b/d</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>94.5%</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>±5.5%</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>Accurately models the seasonal curve: summer hydration surge (Jul-Aug ~650-750 b/d) vs winter baseline (Jan-Feb ~380-480 b/d).</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
